--- a/artfynd/A 9493-2026 artfynd.xlsx
+++ b/artfynd/A 9493-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16910325</v>
+        <v>72476391</v>
       </c>
       <c r="B2" t="n">
-        <v>105123</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220103</v>
+        <v>219788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skärplinge, NO om Skärmarbo, Upl</t>
+          <t>skärplinge, Skärplinge, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652843.0637667924</v>
+        <v>652882</v>
       </c>
       <c r="R2" t="n">
-        <v>6707542.38528026</v>
+        <v>6707567</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-05-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-05-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,26 +762,670 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>åkerkant; vägkant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Linus Söderquist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Linus Söderquist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127475226</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Valnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>653381</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6707586</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>72476386</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>skärplinge, Skärplinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>652882</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6707567</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-07-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-07-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Linus Söderquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linus Söderquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16910325</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skärplinge, NO om Skärmarbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>652843</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6707542</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-05-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-05-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>åkerkant; vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Tommy Knutsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Tommy Knutsson, Jan Edelsjö, Niklas Lönnell</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127475223</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Valnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>652823</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6707571</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127475225</v>
+      </c>
+      <c r="B7" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Valnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>653007</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6707576</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127475227</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Valnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>653470</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6707588</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9493-2026 artfynd.xlsx
+++ b/artfynd/A 9493-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72476391</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127475226</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72476386</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16910325</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127475223</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127475225</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,8 +1461,22 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127475227</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>